--- a/02_加值成品/生物/生物3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物3-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物3-2 人體的循環系統　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物3-2 人體的循環系統　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>推動血液循環的器官是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>血小板</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>心臟</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>骨髓造血補充</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>紅血球</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>幫浦</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>送血離開心臟的血管是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>承受較大壓力</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>動脈</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>靜脈</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>利物質交換</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>離心</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>送血回心臟的血管是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>動脈</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>心臟</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>靜脈</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>骨髓造血補充</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>回心</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>進行物質交換的血管是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>肺循環</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>利物質交換</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>微血管</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>血小板</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>交換</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>血液中運送氧的是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>紅血球</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>心臟</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>骨髓造血補充</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>肺循環</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>運氧</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>血液中負責防禦的是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>白血球</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>心跳</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>獲得氧</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>紅血球</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>防禦</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>血液中幫助凝血的是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>瓣膜</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>心臟</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>血小板</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>體循環</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>凝血</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>心到全身再回心的循環是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>較厚有彈性</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>獲得氧</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>瓣膜</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>體循環</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>全身</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>血液中運送養分與廢物的液體成分是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>血漿</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>血小板</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>靜脈</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>肺循環</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>液體</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>心臟規律收縮舒張形成？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>血漿</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>心跳</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>較厚有彈性</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>白血球</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>幫浦</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物3-2 人體的循環系統　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物3-2 人體的循環系統　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>紅血球運氧靠什麼？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>血紅素</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>血小板</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>紅血球</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>瓣膜</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>攜氧</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>肺循環使血液？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>骨髓造血補充</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>承受較大壓力</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>獲得氧</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>血漿</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>放CO₂取O₂</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>微血管壁薄的意義？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>血紅素</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>心臟</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>利物質交換</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>血漿</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>交換</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>血漿主要運送？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>養分廢物等物質</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>血漿運送紅血球運氧白血球防禦血小板凝血</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>動脈厚耐壓、靜脈有瓣防倒流、微血管薄利交換</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>體循環送含氧血到全身、肺循環到肺換氣</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>液體</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>動脈管壁較厚因為？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>血漿</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>紅血球</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>承受較大壓力</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>血紅素</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>壓力</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>心→肺→心的循環是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>紅血球</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>心臟</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>肺循環</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>微血管</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>肺</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>白血球數量增加常代表？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>身體在對抗感染</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>血漿運送紅血球運氧白血球防禦血小板凝血</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>動脈厚耐壓、靜脈有瓣防倒流、微血管薄利交換</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>體循環送含氧血到全身、肺循環到肺換氣</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>免疫</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>靜脈常有防止血液倒流的？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>靜脈</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>微血管</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>動脈</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>瓣膜</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>防倒流</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>動脈血壓較高所以管壁？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>較厚有彈性</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>紅血球</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>血小板</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>心臟</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>承壓</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>血液循環中氣體交換發生在？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>白血球</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>心臟</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>微血管</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>靜脈</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>交換</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物3-2 人體的循環系統　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物3-2 人體的循環系統　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明體循環與肺循環的路徑與功能？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>養分廢物等物質</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>血漿運送紅血球運氧白血球防禦血小板凝血</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>體循環送含氧血到全身、肺循環到肺換氣</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>規律收縮推動血液循環全身</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>三種血管的構造如何配合其功能？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>血漿運送紅血球運氧白血球防禦血小板凝血</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>動脈厚耐壓、靜脈有瓣防倒流、微血管薄利交換</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>其送血往肺換氣故為缺氧血</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>體循環送含氧血到全身、肺循環到肺換氣</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>配合</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>血液四種成分如何分工？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>血漿運送紅血球運氧白血球防禦血小板凝血</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>加速運送氧與養分至肌肉</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>動脈厚耐壓、靜脈有瓣防倒流、微血管薄利交換</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>管壁薄且遍布組織利氧養分廢物交換</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>分工</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>為何肺動脈運送的是缺氧血？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>其送血往肺換氣故為缺氧血</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>血漿運送紅血球運氧白血球防禦血小板凝血</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>動脈厚耐壓、靜脈有瓣防倒流、微血管薄利交換</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>加速運送氧與養分至肌肉</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>特例</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>微血管在物質交換的關鍵角色？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>管壁薄且遍布組織利氧養分廢物交換</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>動脈厚耐壓、靜脈有瓣防倒流、微血管薄利交換</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>身體在對抗感染</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>血漿運送紅血球運氧白血球防禦血小板凝血</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>關鍵</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>心臟為何被稱為幫浦？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>體循環送含氧血到全身、肺循環到肺換氣</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>管壁薄且遍布組織利氧養分廢物交換</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>血漿運送紅血球運氧白血球防禦血小板凝血</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>規律收縮推動血液循環全身</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>幫浦</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>捐血後身體如何補回血球？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>骨髓造血補充</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>靜脈</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>瓣膜</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>心臟</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>再生</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>循環系統與呼吸消化如何協同？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>體循環送含氧血到全身、肺循環到肺換氣</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>養分廢物等物質</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>血漿運送紅血球運氧白血球防禦血小板凝血</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>運送吸收的養分與交換的氣體到全身</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>協同</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何運動時心跳會加快？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>動脈厚耐壓、靜脈有瓣防倒流、微血管薄利交換</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>體循環送含氧血到全身、肺循環到肺換氣</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>加速運送氧與養分至肌肉</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>身體在對抗感染</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>需求</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>貧血與紅血球或血紅素不足的關係？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>心跳</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>微血管</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>獲得氧</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>攜氧能力下降</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>攜氧</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物3-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>幫浦</t>
+          <t>幫浦：心臟像幫浦一樣規律收縮，把血液推送到全身各處</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>離心</t>
+          <t>離心：動脈是把血液從心臟送往身體各處的血管，方向是離開心臟</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>回心</t>
+          <t>回心：靜脈是把血液從身體各處送回心臟的血管，方向是回到心臟</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>交換</t>
+          <t>交換：微血管管壁很薄，是氧氣、養分和廢物在血液與細胞間交換的地方</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>運氧</t>
+          <t>運氧：紅血球含有血紅素，能攜帶氧氣運送到全身各處</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>防禦</t>
+          <t>防禦：白血球負責吞噬病菌，是身體防禦系統的一員</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>凝血</t>
+          <t>凝血：血小板能幫助血液凝固，讓傷口止血</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>全身</t>
+          <t>全身：血液從心臟出發到全身各處再流回心臟，這條路徑稱為體循環</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>液體</t>
+          <t>液體：血漿是血液中的液態成分，能溶解並運送養分、廢物、激素等物質到全身</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>幫浦</t>
+          <t>幫浦：心臟像幫浦一樣規律地收縮與舒張，把血液推送到全身，這個規律的搏動就是心跳</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>攜氧</t>
+          <t>攜氧：紅血球裡含有血紅素，能與氧結合並把氧氣攜帶到全身</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>放CO₂取O₂</t>
+          <t>放CO₂取O₂：血液流經肺部時會排出二氧化碳並換取新鮮氧氣</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>交換</t>
+          <t>交換：微血管管壁非常薄，方便氧氣、養分和廢物快速進出完成交換</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>液體</t>
+          <t>液體：血漿是血液的液態部分，負責運送養分、廢物等溶在其中的物質</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>壓力</t>
+          <t>壓力：動脈要承受心臟收縮時噴出的高壓血流，所以管壁較厚有彈性</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>肺</t>
+          <t>肺：血液從心臟流到肺再流回心臟，這條路徑稱為肺循環，目的是換氣</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>免疫</t>
+          <t>免疫：白血球數量增加通常代表身體正在對抗細菌或病毒等感染</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>防倒流</t>
+          <t>防倒流：靜脈裡有瓣膜構造，可防止血液因重力而逆流回去</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>承壓</t>
+          <t>承壓：動脈要承受心臟收縮時較高的血壓，因此管壁演化得較厚、較有彈性，才能承受壓力變化</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>交換</t>
+          <t>交換：微血管管壁極薄，是氧氣與二氧化碳等氣體在血液與組織細胞之間進行交換的主要場所</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>循環</t>
+          <t>循環：體循環把含氧血送到全身供細胞使用，肺循環讓血液到肺換氣後帶氧回心臟</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>配合</t>
+          <t>配合：動脈管壁厚耐壓，靜脈有瓣膜防倒流，微血管管壁薄利於物質交換</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>分工</t>
+          <t>分工：血漿負責運送物質，紅血球運氧，白血球防禦病原，血小板幫助凝血</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>特例</t>
+          <t>特例：肺動脈把血液送往肺部換氣前，血中氧氣還很少，所以運送的是缺氧血</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>關鍵</t>
+          <t>關鍵：微血管管壁薄又遍布全身組織，讓氧氣、養分和廢物能順利交換</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>幫浦</t>
+          <t>幫浦：心臟藉由規律收縮與舒張，像幫浦一樣不斷把血液推送到全身</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>再生</t>
+          <t>再生：捐血後骨髓會加速製造新的血球，補回流失的血液成分</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>協同</t>
+          <t>協同：循環系統把消化吸收的養分和呼吸交換的氣體一起運送到全身利用</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>需求</t>
+          <t>需求：運動時肌肉消耗更多氧氣與養分，心臟必須加快跳動速率，才能把足夠的血液更快送到肌肉，滿足身體需求</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>攜氧</t>
+          <t>攜氧：紅血球內的血紅素負責攜帶氧氣，若紅血球數量或血紅素不足，血液攜氧能力下降，就會造成貧血症狀</t>
         </is>
       </c>
     </row>
